--- a/光伏配储项目/电价数据/2026/吉祥站.xlsx
+++ b/光伏配储项目/电价数据/2026/吉祥站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.60338</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.80824</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6792100000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6081599999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.59187</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.59266</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43514</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43218</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40621</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42731</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51778</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.20073</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22201</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21622</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17767</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20247</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15992</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2434</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24129</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24606</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23056</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.22815</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.9149299999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.22466</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.52413</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.5398200000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5255599999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60481</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.60462</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72601</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.21261</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.77151</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42971</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43482</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65443</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.93201</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53715</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.27381</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.38843</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.14201</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24136</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34811</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.51071</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.51163</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75185</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8035599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.31107</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.12195</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86542</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75346</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51437</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46441</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41437</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42381</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.7444</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86236</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.90308</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48902</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5069</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49662</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49681</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47946</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.69485</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55264</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.6546000000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50951</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5833400000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85842</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07415</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.58478</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.93716</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.89125</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5612699999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.25328</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05811</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50318</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5875499999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54718</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.53867</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8596200000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6048300000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76977</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8371499999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.21076</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.79884</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15829</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.87693</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.26111</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1654</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.32422</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10578</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.1501</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7089099999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04097</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.89351</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05131</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9592999999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.07354</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.87778</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.8146100000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83472</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44083</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33431</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50234</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48254</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43865</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46714</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.17947</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27183</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15866</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.5498200000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.49555</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.49001</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.57996</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.58693</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.66739</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.63397</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.90013</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.59187</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.77934</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.86658</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52228</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.52366</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.77719</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72276</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64471</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6374099999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50043</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.58824</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50357</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51156</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5776100000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6117400000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.58052</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6020800000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23368</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6099600000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.73527</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5106700000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57802</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.71758</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7171799999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45522</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59705</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5485599999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60114</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.72909</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.87079</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6974</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.57877</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5152899999999999</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64711</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45409</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3416</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51362</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49133</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43864</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44504</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.46284</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46675</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.63806</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.48801</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.00323</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59177</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49235</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.64818</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48215</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45557</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.46966</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.53387</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.65864</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.51474</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.71088</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5556599999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.52008</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50203</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47932</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45525</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30937</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.04616</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24813</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.23924</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.23581</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.19143</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25445</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22396</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08622</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.14886</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01488</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44755</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45452</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3298</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24413</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21017</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.09143000000000001</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22045</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.25975</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24103</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25387</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10344</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01138</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2088</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19439</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19955</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.03339</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06295000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06116</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32309</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30067</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7849400000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87105</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.70513</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.59096</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5013299999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5593400000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.86921</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46063</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49232</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.6928799999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83339</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48728</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57668</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.48773</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23004</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28454</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.90454</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23862</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1942</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27471</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24017</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26088</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27811</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2840299999999999</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26823</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41162</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.40406</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81172</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38461</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08569</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65388</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7428400000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46777</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22841</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.05887</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24472</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02938</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24592</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6647799999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27227</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27796</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22108</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.22935</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23658</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21158</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25521</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2034</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20391</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.08982999999999999</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22294</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26329</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.09076000000000001</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24788</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26126</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.2473</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15616</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20096</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23748</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23914</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24162</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24852</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22231</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22509</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24149</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27359</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24176</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26765</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24985</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22064</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.2374</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.2404</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24093</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30633</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23659</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.50783</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41914</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32604</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22208</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.47018</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.44224</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.55267</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5323600000000001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.43014</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.50096</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.57053</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.48889</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.43979</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.66484</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.83877</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.5766100000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.46465</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.54184</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.5081</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.49432</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.67095</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.50374</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.51544</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.53608</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.5592200000000001</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.43853</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.45671</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.69559</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.51425</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.51318</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48885</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47056</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7487</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.46214</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.46857</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49056</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22406</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.15103</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24825</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24589</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24294</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21853</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24267</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24796</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25881</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25793</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23579</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22457</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26384</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.26088</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33087</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.12479</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63979</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.84126</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.48402</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.49128</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.6301599999999999</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5678799999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.69786</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.65538</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7297400000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84872</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.44727</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.6874400000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.58738</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.54132</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.45223</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5347999999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.41473</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33141</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47837</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47301</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.45627</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.50378</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.54064</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.61236</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.61972</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43866</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.68728</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.86956</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.45594</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.46362</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.5126900000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.60023</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5206900000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5302</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75462</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6067400000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6537500000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.13967</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.53328</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.13762</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.46163</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46531</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.46578</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.24127</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25298</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23346</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26363</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25316</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26402</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23903</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23555</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.13669</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.12754</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23424</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.12075</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25363</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23318</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.12051</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22058</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22662</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24885</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22342</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22697</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23052</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.11664</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23407</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.11614</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.10024</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.24831</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23173</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21076</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.09165000000000001</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27671</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11319</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24691</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01567</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.18615</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24912</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25462</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26666</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.2438</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.22898</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.22791</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.26972</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26267</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.14825</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23533</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23167</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.10486</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24157</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25624</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.13349</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.09841</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.10707</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10706</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10636</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23665</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.09643</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.10548</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22531</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.09838</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.10973</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07052</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25518</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.11361</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00204</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14161</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01601</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02933</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00092</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03846</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02227</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03637</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26441</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27774</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.10819</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.29898</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.52477</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.20621</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24066</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23259</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23765</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22954</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21507</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11566</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.07787000000000001</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.09462000000000001</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.10527</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.11921</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.08439000000000001</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.13089</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.13751</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.14964</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27065</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.10489</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.55791</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86752</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85898</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10685</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.09720999999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.16609</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.13562</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00063</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06667000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47346</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.08217</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.65842</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.55443</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.59496</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.07185</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97323</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.5634400000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.72293</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.6102000000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8301000000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82831</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8325900000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93033</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.5522999999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.60623</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3337</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.46586</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.43621</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48195</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26811</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26373</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.23651</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25239</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.22929</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23273</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.11186</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.24428</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.5626599999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32227</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.48023</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.70773</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.45783</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47599</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.53674</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.44465</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46996</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.71474</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.84973</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.1205</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.48498</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5611900000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.57392</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.02939</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8859900000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.53516</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64558</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.48815</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.46004</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.43015</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22349</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34036</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43595</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43478</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.43891</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50419</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5905900000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.24845</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.02286</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.65073</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.8732000000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51881</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.64611</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.58117</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.74058</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.9853999999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.88844</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.79936</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.72411</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46976</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34482</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.14067</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.46796</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.49246</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.77588</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.42268</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.5619299999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44618</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.7777200000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.48109</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.43391</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.48534</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.44777</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.52863</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.66391</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44599</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.51789</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.48161</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.65142</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47691</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.49329</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35069</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.90928</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.47289</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5268999999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49248</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.49912</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40716</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.50629</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41469</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.50342</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.58327</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.44872</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35163</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17583</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14324</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04575</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12086</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22493</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14739</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14401</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19194</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22645</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15181</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15412</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19587</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14058</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.49763</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43321</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.54242</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45598</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37891</v>
       </c>
     </row>
   </sheetData>
